--- a/analysis/Mixed_Metabolic_Cohort/DPP_Metformin_2012_extracted.xlsx
+++ b/analysis/Mixed_Metabolic_Cohort/DPP_Metformin_2012_extracted.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +192,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -222,6 +268,276 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>51</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,67 +890,67 @@
           <t>STUDY &amp; INTERVENTION ARMS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="12" t="n"/>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ELIGIBILITY CRITERIA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
-      <c r="AA1" s="1" t="n"/>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
+      <c r="N1" s="11" t="n"/>
+      <c r="O1" s="11" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="11" t="n"/>
+      <c r="R1" s="11" t="n"/>
+      <c r="S1" s="11" t="n"/>
+      <c r="T1" s="11" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="11" t="n"/>
+      <c r="W1" s="11" t="n"/>
+      <c r="X1" s="11" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="11" t="n"/>
+      <c r="AA1" s="11" t="n"/>
+      <c r="AB1" s="11" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="12" t="n"/>
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>POPULATION STRATIFICATION</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="n"/>
-      <c r="AG1" s="1" t="n"/>
-      <c r="AH1" s="1" t="n"/>
+      <c r="AF1" s="11" t="n"/>
+      <c r="AG1" s="11" t="n"/>
+      <c r="AH1" s="12" t="n"/>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>CLINICAL VARIABLES &amp; OUTCOMES</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="n"/>
-      <c r="AK1" s="1" t="n"/>
-      <c r="AL1" s="1" t="n"/>
-      <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="n"/>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
-      <c r="AS1" s="1" t="n"/>
-      <c r="AT1" s="1" t="n"/>
-      <c r="AU1" s="1" t="n"/>
-      <c r="AV1" s="1" t="n"/>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="n"/>
+      <c r="AJ1" s="11" t="n"/>
+      <c r="AK1" s="11" t="n"/>
+      <c r="AL1" s="11" t="n"/>
+      <c r="AM1" s="11" t="n"/>
+      <c r="AN1" s="11" t="n"/>
+      <c r="AO1" s="11" t="n"/>
+      <c r="AP1" s="11" t="n"/>
+      <c r="AQ1" s="11" t="n"/>
+      <c r="AR1" s="11" t="n"/>
+      <c r="AS1" s="11" t="n"/>
+      <c r="AT1" s="11" t="n"/>
+      <c r="AU1" s="11" t="n"/>
+      <c r="AV1" s="11" t="n"/>
+      <c r="AW1" s="11" t="n"/>
+      <c r="AX1" s="12" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -672,7 +988,7 @@
           <t>Period of Study</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
+      <c r="H2" s="12" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Total Cohort (N)</t>
@@ -688,37 +1004,37 @@
           <t>Age</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="12" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Bmi</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="11" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="12" t="n"/>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Baseline Fasting Glucose</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
+      <c r="V2" s="11" t="n"/>
+      <c r="W2" s="11" t="n"/>
+      <c r="X2" s="11" t="n"/>
+      <c r="Y2" s="12" t="n"/>
       <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Baseline Impaired Glucose Tolerance</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
+      <c r="AA2" s="11" t="n"/>
+      <c r="AB2" s="11" t="n"/>
+      <c r="AC2" s="11" t="n"/>
+      <c r="AD2" s="12" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Race / Ethnicity</t>
@@ -734,39 +1050,39 @@
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n"/>
+      <c r="AH2" s="12" t="n"/>
       <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="n"/>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="2" t="n"/>
+      <c r="AJ2" s="11" t="n"/>
+      <c r="AK2" s="11" t="n"/>
+      <c r="AL2" s="12" t="n"/>
       <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="n"/>
-      <c r="AO2" s="2" t="n"/>
-      <c r="AP2" s="2" t="n"/>
+      <c r="AN2" s="11" t="n"/>
+      <c r="AO2" s="11" t="n"/>
+      <c r="AP2" s="12" t="n"/>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="n"/>
-      <c r="AS2" s="2" t="n"/>
-      <c r="AT2" s="2" t="n"/>
+      <c r="AR2" s="11" t="n"/>
+      <c r="AS2" s="11" t="n"/>
+      <c r="AT2" s="12" t="n"/>
       <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="n"/>
-      <c r="AW2" s="2" t="n"/>
-      <c r="AX2" s="2" t="n"/>
+      <c r="AV2" s="11" t="n"/>
+      <c r="AW2" s="11" t="n"/>
+      <c r="AX2" s="12" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
@@ -2827,8 +3143,8 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="AU2:AX2"/>
     <mergeCell ref="AI1:AX1"/>
-    <mergeCell ref="AU2:AX2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="U2:Y2"/>
     <mergeCell ref="Z2:AD2"/>
@@ -2842,6 +3158,7 @@
     <mergeCell ref="AE1:AH1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2988,6 +3305,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3176,6 +3494,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3508,6 +3827,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5134,6 +5454,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6160,6 +6481,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6226,6 +6548,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7572,6 +7895,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8094,5 +8418,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>